--- a/extracted/reports/tramos_filtrado_estricto/tramo_214+580_214+630.xlsx
+++ b/extracted/reports/tramos_filtrado_estricto/tramo_214+580_214+630.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F179"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -485,14 +485,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Filtro estricto: INICIO (KM) y FIN (KM) contenidos en el tramo | Total registros: 158</t>
+          <t>Filtro: FIN completo contenido en tramo; FIN en blanco si INICIO cae en tramo | Total registros: 172</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Año 2018 (36 registros)</t>
+          <t>Año 2018 (38 registros)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1046,17 +1046,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>2018-06-02</t>
+          <t>2018-05-20</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1064,29 +1064,25 @@
           <t>214+600</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
+      <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza de juntas de cuneta de vía</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>2018-06-17</t>
+          <t>2018-05-20</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1094,13 +1090,9 @@
           <t>214+600</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>214+630</t>
-        </is>
-      </c>
+      <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n">
-        <v>30</v>
+        <v>9.066666666666666</v>
       </c>
     </row>
     <row r="25">
@@ -1116,7 +1108,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2018-06-02</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1146,12 +1138,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2018-06-17</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1160,7 +1152,7 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -1176,7 +1168,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1190,13 +1182,13 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Repintado de Parapetos Muros T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1206,21 +1198,21 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2018-06-24</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>214+595</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -1236,7 +1228,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1246,7 +1238,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
@@ -1256,7 +1248,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Repintado de Parapetos Muros T2</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -1266,77 +1258,77 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>2018-08-05</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+595</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>30</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-04</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>2018-08-10</t>
+          <t>2018-08-05</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
@@ -1356,12 +1348,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>2018-08-18</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -1370,53 +1362,53 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>20</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>2018-08-25</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+590</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2018-08-26</t>
+          <t>2018-08-18</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1430,7 +1422,7 @@
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -1446,12 +1438,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>2018-08-30</t>
+          <t>2018-08-25</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -1460,7 +1452,7 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -1476,7 +1468,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>2018-09-16</t>
+          <t>2018-08-26</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1486,27 +1478,27 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>2018-09-16</t>
+          <t>2018-08-30</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1516,11 +1508,11 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>214+610</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
@@ -1536,7 +1528,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2018-09-16</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1546,27 +1538,27 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>2018-09-29</t>
+          <t>2018-09-16</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1576,11 +1568,11 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+610</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -1596,141 +1588,141 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de carril/pista y bermas T2</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de carril/pista y bermas T2</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="n">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Año 2019 (18 registros)</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>INICIO (KM)</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>FIN (KM)</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>METRADO</t>
         </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>2018-12-28</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>214+630</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>2019-02-01</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>214+630</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>144</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>2019-02-03</t>
+          <t>2018-12-28</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -1740,11 +1732,11 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>214+610</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47">
@@ -1760,37 +1752,37 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>2019-02-20</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>20</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2019-02-03</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -1800,27 +1792,27 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+610</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>2019-03-04</t>
+          <t>2019-02-20</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -1834,7 +1826,7 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -1850,7 +1842,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -1864,23 +1856,23 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>2019-03-09</t>
+          <t>2019-03-04</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -1894,7 +1886,7 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52">
@@ -1910,51 +1902,51 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2019-03-19</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>480</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>2019-03-19</t>
+          <t>2019-03-09</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54">
@@ -1984,7 +1976,7 @@
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>90</v>
+        <v>480</v>
       </c>
     </row>
     <row r="55">
@@ -2014,18 +2006,18 @@
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -2035,27 +2027,27 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -2065,46 +2057,46 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2019-03-19</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59">
@@ -2120,7 +2112,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2019-03-19</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2140,165 +2132,165 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>2019-11-03</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
+          <t>Limpieza de carril/pista y bermas T2</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>2019-05-11</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>2019-11-03</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>214+630</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
           <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>2019-11-04</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>214+580</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>214+590</t>
         </is>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F63" s="5" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Año 2020 (13 registros)</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="n"/>
-      <c r="F62" s="2" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Año 2020 (15 registros)</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>INICIO (KM)</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>FIN (KM)</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>METRADO</t>
         </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>2020-01-18</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>214+610</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza Manual de Cuerpo de Alcantarilla T2</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>2020-02-03</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>214+580</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>214+590</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -2314,247 +2306,239 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>2020-02-03</t>
+          <t>2020-01-18</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+610</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuerpo de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2020-02-03</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+590</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>2020-05-16</t>
+          <t>2020-02-03</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>214+624</t>
+          <t>214+590</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Reparación Parcial de Guarda Vías T2</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>214+630</t>
-        </is>
-      </c>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n"/>
       <c r="F69" s="5" t="n">
-        <v>33.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Reposición de capta faros (ojo de gato) T2</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>214+610</t>
-        </is>
-      </c>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n"/>
       <c r="F70" s="5" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
+          <t>2020-05-13</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>2020-11-21</t>
+          <t>2020-05-16</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+624</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>60</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>2020-11-22</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>30</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>2020-11-29</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -2564,311 +2548,307 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+610</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Juntas en Cunetas y Bermas</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>2020-11-29</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+590</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>11.33333333333333</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>2020-11-21</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>214+590</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>2020-11-22</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>214+590</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>2020-12-02</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>214+580</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>214+585</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Año 2021 (34 registros)</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="n"/>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="n"/>
-      <c r="F77" s="2" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>2020-11-29</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza de Juntas en Cunetas y Bermas</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>2021-02-05</t>
+          <t>2020-11-29</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>30</v>
+        <v>11.33333333333333</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>2021-02-20</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+585</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>2021-02-20</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>214+605</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>12</v>
-      </c>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Año 2021 (38 registros)</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>2021-02-21</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>214+610</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>214+630</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>72</v>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
+          <t>2021-01-31</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>214+610</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>214+615</t>
-        </is>
-      </c>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n"/>
       <c r="F83" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>2021-04-24</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+590</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+590</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-02-20</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -2882,13 +2862,13 @@
         </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Juntas en Cunetas y Bermas</t>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -2898,7 +2878,7 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-02-20</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -2908,177 +2888,177 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+605</t>
         </is>
       </c>
       <c r="F86" s="5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuerpo de Alcantarilla T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-02-21</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+610</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+610</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+615</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>2021-06-12</t>
+          <t>2021-04-24</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>195</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de Juntas en Cunetas y Bermas</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+          <t>Limpieza Manual de Cuerpo de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -3088,27 +3068,27 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+590</t>
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -3122,13 +3102,13 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -3138,7 +3118,7 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>2021-06-27</t>
+          <t>2021-06-12</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -3152,7 +3132,7 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>15</v>
+        <v>195</v>
       </c>
     </row>
     <row r="95">
@@ -3168,7 +3148,7 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -3182,28 +3162,28 @@
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>405</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -3212,13 +3192,13 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -3228,7 +3208,7 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -3238,27 +3218,27 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -3272,13 +3252,13 @@
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -3288,7 +3268,7 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -3302,43 +3282,43 @@
         </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Residuos Solidos / Basuras</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F100" s="5" t="n">
-        <v>30</v>
+        <v>405</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Residuos Solidos / Basuras</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -3348,7 +3328,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -3368,17 +3348,17 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -3388,32 +3368,32 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>214+596</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>2021-08-08</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -3422,28 +3402,28 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>2021-08-26</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -3458,77 +3438,73 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza Residuos Solidos / Basuras</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
-        <v>160</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>2021-09-05</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n"/>
       <c r="F106" s="5" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+          <t>Limpieza Residuos Solidos / Basuras</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -3548,61 +3524,61 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+596</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuerpo de Alcantarilla T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
+          <t>2021-08-08</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="110">
@@ -3618,7 +3594,7 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-08-26</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -3632,7 +3608,7 @@
         </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111">
@@ -3648,7 +3624,7 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -3662,171 +3638,179 @@
         </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>15</v>
+        <v>160</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>2021-09-05</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
           <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
-      <c r="B112" s="5" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>2021-11-12</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
-        <is>
-          <t>214+590</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
-      <c r="F112" s="5" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Año 2022 (16 registros)</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="n"/>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n"/>
-      <c r="E113" s="2" t="n"/>
-      <c r="F113" s="2" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuerpo de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>2022-01-15</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n"/>
       <c r="F115" s="5" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuerpo de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>2022-02-06</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+590</t>
         </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+          <t>Reposición de Señalización Vertical T2</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>2022-02-12</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
+          <t>214+629</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n"/>
       <c r="F117" s="5" t="n">
-        <v>70</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="118">
@@ -3842,7 +3826,7 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -3862,31 +3846,31 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+590</t>
         </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120">
@@ -3902,12 +3886,12 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+590</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -3916,83 +3900,67 @@
         </is>
       </c>
       <c r="F120" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>2022-07-31</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="n">
-        <v>20</v>
-      </c>
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Año 2022 (18 registros)</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>20</v>
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
+          <t>2022-01-15</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
@@ -4006,23 +3974,23 @@
         </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Juntas en Cunetas y Bermas</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
+          <t>2022-02-06</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -4036,23 +4004,23 @@
         </is>
       </c>
       <c r="F124" s="5" t="n">
-        <v>11.33333333333333</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>2022-09-05</t>
+          <t>2022-02-12</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -4062,41 +4030,41 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F125" s="5" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>214+584</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F126" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127">
@@ -4112,7 +4080,7 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -4122,27 +4090,27 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F127" s="5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>2022-12-10</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -4152,27 +4120,27 @@
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F128" s="5" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>2022-12-11</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -4202,7 +4170,7 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>2022-12-20</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
@@ -4220,63 +4188,79 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>Año 2023 (7 registros)</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="n"/>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n"/>
-      <c r="E131" s="2" t="n"/>
-      <c r="F131" s="2" t="n"/>
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>2022-09-04</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F132" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Juntas en Cunetas y Bermas</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>2022-09-04</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>11.33333333333333</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>2022-12-24</t>
+          <t>2022-09-05</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -4286,57 +4270,57 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>214+610</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F133" s="5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>214+610</t>
+          <t>214+580</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+584</t>
         </is>
       </c>
       <c r="F134" s="5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -4346,47 +4330,43 @@
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F135" s="5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2022-11-25</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>214+630</t>
-        </is>
-      </c>
+          <t>214+610</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n"/>
       <c r="F136" s="5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza Manual de Cuerpo de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
@@ -4396,37 +4376,33 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2022-12-06</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>214+630</t>
-        </is>
-      </c>
+          <t>214+610</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n"/>
       <c r="F137" s="5" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2022-12-10</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -4436,27 +4412,27 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>214+610</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F138" s="5" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2022-12-11</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -4466,101 +4442,101 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F139" s="5" t="n">
-        <v>285</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Año 2024 (16 registros)</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="n"/>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n"/>
-      <c r="E140" s="2" t="n"/>
-      <c r="F140" s="2" t="n"/>
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de carril/pista y bermas T2</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>2022-12-20</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Año 2023 (7 registros)</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="n"/>
+      <c r="F141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>INICIO (KM)</t>
         </is>
       </c>
-      <c r="E141" s="3" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>FIN (KM)</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>METRADO</t>
         </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>Remocion de Derrumbes T2</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>2023-12-27</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>214+630</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>2023-12-30</t>
+          <t>2022-12-24</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
@@ -4570,32 +4546,32 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+610</t>
         </is>
       </c>
       <c r="F143" s="5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+610</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -4610,17 +4586,17 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
@@ -4630,27 +4606,27 @@
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F145" s="5" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
@@ -4664,23 +4640,23 @@
         </is>
       </c>
       <c r="F146" s="5" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
@@ -4694,13 +4670,13 @@
         </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -4710,7 +4686,7 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
@@ -4720,27 +4696,27 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+610</t>
         </is>
       </c>
       <c r="F148" s="5" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -4754,67 +4730,51 @@
         </is>
       </c>
       <c r="F149" s="5" t="n">
-        <v>60</v>
+        <v>285</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="4" t="inlineStr">
-        <is>
-          <t>Remocion de Derrumbes T2</t>
-        </is>
-      </c>
-      <c r="B150" s="5" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>2024-02-17</t>
-        </is>
-      </c>
-      <c r="D150" s="5" t="inlineStr">
-        <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
-      <c r="F150" s="5" t="n">
-        <v>60</v>
-      </c>
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Año 2024 (20 registros)</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="n"/>
+      <c r="F150" s="2" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>Remocion de Derrumbes T2</t>
-        </is>
-      </c>
-      <c r="B151" s="5" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C151" s="5" t="inlineStr">
-        <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="D151" s="5" t="inlineStr">
-        <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
-      <c r="F151" s="5" t="n">
-        <v>135</v>
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -4830,7 +4790,7 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
@@ -4840,27 +4800,27 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F152" s="5" t="n">
-        <v>105</v>
+        <v>150</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2023-12-30</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
@@ -4870,27 +4830,27 @@
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F153" s="5" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
@@ -4900,27 +4860,27 @@
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F154" s="5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuerpo de Alcantarilla T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
@@ -4930,11 +4890,11 @@
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>214+610</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F155" s="5" t="n">
-        <v>14</v>
+        <v>90</v>
       </c>
     </row>
     <row r="156">
@@ -4950,7 +4910,7 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-01-07</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
@@ -4960,91 +4920,107 @@
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F156" s="5" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
+          <t>Remocion de Derrumbes T2</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>2024-01-30</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>214+630</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>Remocion de Derrumbes T2</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>214+630</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
           <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
-      <c r="B157" s="5" t="inlineStr">
+      <c r="B159" s="5" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
-      <c r="C157" s="5" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="inlineStr">
-        <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
         <is>
           <t>214+630</t>
         </is>
       </c>
-      <c r="F157" s="5" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>Año 2025 (13 registros)</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="n"/>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n"/>
-      <c r="E158" s="2" t="n"/>
-      <c r="F158" s="2" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F159" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="F159" s="5" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
@@ -5054,81 +5030,81 @@
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F160" s="5" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F161" s="5" t="n">
-        <v>50</v>
+        <v>135</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F162" s="5" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
     </row>
     <row r="163">
@@ -5144,21 +5120,21 @@
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F163" s="5" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
     </row>
     <row r="164">
@@ -5174,102 +5150,102 @@
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>214+600</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F164" s="5" t="n">
-        <v>180</v>
+        <v>15</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuerpo de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>214+630</t>
+          <t>214+610</t>
         </is>
       </c>
       <c r="F165" s="5" t="n">
-        <v>200</v>
+        <v>14</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>214+590</t>
+          <t>214+620</t>
         </is>
       </c>
       <c r="F166" s="5" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
+          <t>214+600</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -5278,73 +5254,65 @@
         </is>
       </c>
       <c r="F167" s="5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
+          <t>Reparación de las Estructuras de Contención (gabión) T2</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="inlineStr">
-        <is>
-          <t>214+630</t>
-        </is>
-      </c>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="n"/>
       <c r="F168" s="5" t="n">
-        <v>14</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Cajas de Inspección Subdren T2</t>
+          <t>Tratamiento de Fisuras T2</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>214+630</t>
-        </is>
-      </c>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="n"/>
       <c r="F169" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual / Mecanizada T2</t>
+          <t>Limpieza de Superfície de Concreto y Dispos. Drenaje T2</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
@@ -5354,141 +5322,133 @@
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>214+580</t>
-        </is>
-      </c>
-      <c r="E170" s="5" t="inlineStr">
-        <is>
-          <t>214+630</t>
-        </is>
-      </c>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n"/>
       <c r="F170" s="5" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="n"/>
+      <c r="F171" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Año 2025 (13 registros)</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="n"/>
+      <c r="F172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
           <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
-      <c r="B171" s="5" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C171" s="5" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="D171" s="5" t="inlineStr">
-        <is>
-          <t>214+580</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="inlineStr">
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
         <is>
           <t>214+590</t>
         </is>
       </c>
-      <c r="F171" s="5" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
-        </is>
-      </c>
-      <c r="B172" s="5" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C172" s="5" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="D172" s="5" t="inlineStr">
-        <is>
-          <t>214+580</t>
-        </is>
-      </c>
-      <c r="E172" s="5" t="inlineStr">
-        <is>
-          <t>214+620</t>
-        </is>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Año 2026 (5 registros)</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="n"/>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n"/>
-      <c r="E173" s="2" t="n"/>
-      <c r="F173" s="2" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
@@ -5498,27 +5458,27 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>214+620</t>
+          <t>214+630</t>
         </is>
       </c>
       <c r="F175" s="5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
@@ -5532,13 +5492,13 @@
         </is>
       </c>
       <c r="F176" s="5" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
@@ -5548,7 +5508,7 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
@@ -5562,7 +5522,7 @@
         </is>
       </c>
       <c r="F177" s="5" t="n">
-        <v>30</v>
+        <v>225</v>
       </c>
     </row>
     <row r="178">
@@ -5578,7 +5538,7 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
@@ -5592,52 +5552,456 @@
         </is>
       </c>
       <c r="F178" s="5" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
+          <t>Limpieza de carril/pista y bermas T2</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>214+630</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
+        <is>
+          <t>214+590</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>214+630</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>214+630</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Cajas de Inspección Subdren T2</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>214+630</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual / Mecanizada T2</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>214+630</t>
+        </is>
+      </c>
+      <c r="F184" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>214+590</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de carril/pista y bermas T2</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Año 2026 (5 registros)</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="n"/>
+      <c r="C187" s="2" t="n"/>
+      <c r="D187" s="2" t="n"/>
+      <c r="E187" s="2" t="n"/>
+      <c r="F187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>214+620</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>214+590</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
           <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
-      <c r="B179" s="5" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C179" s="5" t="inlineStr">
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>214+580</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>Remocion de Derrumbes T2</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="D193" s="5" t="inlineStr">
         <is>
           <t>214+580</t>
         </is>
       </c>
-      <c r="E179" s="5" t="inlineStr">
-        <is>
-          <t>214+600</t>
-        </is>
-      </c>
-      <c r="F179" s="5" t="n">
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>214+600</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="n">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A172:F172"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A173:F173"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A141:F141"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A140:F140"/>
-    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A187:F187"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A81:F81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
